--- a/Team-Data/2012-13/3-26-2012-13.xlsx
+++ b/Team-Data/2012-13/3-26-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>0.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE2" t="n">
         <v>11</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-26-2012-13</t>
+          <t>2013-03-26</t>
         </is>
       </c>
     </row>
@@ -843,25 +910,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E3" t="n">
         <v>36</v>
       </c>
       <c r="F3" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G3" t="n">
-        <v>0.514</v>
+        <v>0.522</v>
       </c>
       <c r="H3" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="I3" t="n">
-        <v>36.7</v>
+        <v>36.8</v>
       </c>
       <c r="J3" t="n">
-        <v>79.7</v>
+        <v>79.8</v>
       </c>
       <c r="K3" t="n">
         <v>0.461</v>
@@ -870,7 +937,7 @@
         <v>6</v>
       </c>
       <c r="M3" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="N3" t="n">
         <v>0.356</v>
@@ -882,7 +949,7 @@
         <v>21.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.778</v>
+        <v>0.779</v>
       </c>
       <c r="R3" t="n">
         <v>8.199999999999999</v>
@@ -894,34 +961,34 @@
         <v>39.7</v>
       </c>
       <c r="U3" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="V3" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="W3" t="n">
         <v>8.4</v>
       </c>
       <c r="X3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y3" t="n">
         <v>4.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA3" t="n">
         <v>19.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>96</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="AE3" t="n">
         <v>14</v>
@@ -951,7 +1018,7 @@
         <v>27</v>
       </c>
       <c r="AN3" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AO3" t="n">
         <v>18</v>
@@ -972,7 +1039,7 @@
         <v>29</v>
       </c>
       <c r="AU3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AV3" t="n">
         <v>13</v>
@@ -984,13 +1051,13 @@
         <v>24</v>
       </c>
       <c r="AY3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ3" t="n">
         <v>27</v>
       </c>
       <c r="BA3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BB3" t="n">
         <v>18</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-26-2012-13</t>
+          <t>2013-03-26</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>1.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE4" t="n">
         <v>9</v>
@@ -1151,7 +1218,7 @@
         <v>21</v>
       </c>
       <c r="AT4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU4" t="n">
         <v>28</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-26-2012-13</t>
+          <t>2013-03-26</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-9.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE5" t="n">
         <v>30</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-26-2012-13</t>
+          <t>2013-03-26</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>0.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
@@ -1482,7 +1549,7 @@
         <v>15</v>
       </c>
       <c r="AI6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ6" t="n">
         <v>15</v>
@@ -1500,10 +1567,10 @@
         <v>26</v>
       </c>
       <c r="AO6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ6" t="n">
         <v>6</v>
@@ -1536,7 +1603,7 @@
         <v>12</v>
       </c>
       <c r="BA6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB6" t="n">
         <v>29</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-26-2012-13</t>
+          <t>2013-03-26</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-4.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE7" t="n">
         <v>28</v>
@@ -1661,7 +1728,7 @@
         <v>28</v>
       </c>
       <c r="AH7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI7" t="n">
         <v>19</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-26-2012-13</t>
+          <t>2013-03-26</t>
         </is>
       </c>
     </row>
@@ -1753,19 +1820,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E8" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F8" t="n">
         <v>36</v>
       </c>
       <c r="G8" t="n">
-        <v>0.493</v>
+        <v>0.486</v>
       </c>
       <c r="H8" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
       <c r="I8" t="n">
         <v>38.7</v>
@@ -1777,22 +1844,22 @@
         <v>0.461</v>
       </c>
       <c r="L8" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="M8" t="n">
         <v>20.1</v>
       </c>
       <c r="N8" t="n">
-        <v>0.374</v>
+        <v>0.376</v>
       </c>
       <c r="O8" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="P8" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.795</v>
+        <v>0.794</v>
       </c>
       <c r="R8" t="n">
         <v>9.300000000000001</v>
@@ -1810,7 +1877,7 @@
         <v>14.2</v>
       </c>
       <c r="W8" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="X8" t="n">
         <v>5.4</v>
@@ -1825,22 +1892,22 @@
         <v>19.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>101.8</v>
+        <v>101.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="AE8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF8" t="n">
         <v>17</v>
       </c>
       <c r="AG8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AH8" t="n">
         <v>3</v>
@@ -1867,7 +1934,7 @@
         <v>16</v>
       </c>
       <c r="AP8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ8" t="n">
         <v>2</v>
@@ -1897,7 +1964,7 @@
         <v>4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA8" t="n">
         <v>23</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-26-2012-13</t>
+          <t>2013-03-26</t>
         </is>
       </c>
     </row>
@@ -2019,10 +2086,10 @@
         <v>4</v>
       </c>
       <c r="AF9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH9" t="n">
         <v>7</v>
@@ -2046,7 +2113,7 @@
         <v>24</v>
       </c>
       <c r="AO9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP9" t="n">
         <v>3</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-26-2012-13</t>
+          <t>2013-03-26</t>
         </is>
       </c>
     </row>
@@ -2117,25 +2184,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E10" t="n">
         <v>24</v>
       </c>
       <c r="F10" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G10" t="n">
-        <v>0.333</v>
+        <v>0.338</v>
       </c>
       <c r="H10" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I10" t="n">
-        <v>36</v>
+        <v>36.1</v>
       </c>
       <c r="J10" t="n">
-        <v>81.2</v>
+        <v>81.3</v>
       </c>
       <c r="K10" t="n">
         <v>0.444</v>
@@ -2150,25 +2217,25 @@
         <v>0.356</v>
       </c>
       <c r="O10" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="P10" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.698</v>
+        <v>0.696</v>
       </c>
       <c r="R10" t="n">
         <v>12.2</v>
       </c>
       <c r="S10" t="n">
-        <v>30.2</v>
+        <v>30.3</v>
       </c>
       <c r="T10" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
       <c r="U10" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="V10" t="n">
         <v>15</v>
@@ -2180,34 +2247,34 @@
         <v>5.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z10" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AA10" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AB10" t="n">
-        <v>94</v>
+        <v>94.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>-4.9</v>
+        <v>-4.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE10" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF10" t="n">
         <v>26</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>27</v>
       </c>
       <c r="AG10" t="n">
         <v>26</v>
       </c>
       <c r="AH10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI10" t="n">
         <v>23</v>
@@ -2216,16 +2283,16 @@
         <v>22</v>
       </c>
       <c r="AK10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM10" t="n">
         <v>24</v>
       </c>
       <c r="AN10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO10" t="n">
         <v>23</v>
@@ -2240,10 +2307,10 @@
         <v>10</v>
       </c>
       <c r="AS10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU10" t="n">
         <v>23</v>
@@ -2261,13 +2328,13 @@
         <v>20</v>
       </c>
       <c r="AZ10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA10" t="n">
         <v>15</v>
       </c>
       <c r="BB10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC10" t="n">
         <v>26</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-26-2012-13</t>
+          <t>2013-03-26</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2456,7 @@
         <v>10</v>
       </c>
       <c r="AH11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI11" t="n">
         <v>9</v>
@@ -2446,7 +2513,7 @@
         <v>28</v>
       </c>
       <c r="BA11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB11" t="n">
         <v>9</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-26-2012-13</t>
+          <t>2013-03-26</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>3.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE12" t="n">
         <v>11</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-26-2012-13</t>
+          <t>2013-03-26</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>4.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE13" t="n">
         <v>7</v>
@@ -2750,7 +2817,7 @@
         <v>8</v>
       </c>
       <c r="AG13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH13" t="n">
         <v>12</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-26-2012-13</t>
+          <t>2013-03-26</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E14" t="n">
         <v>48</v>
       </c>
       <c r="F14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G14" t="n">
-        <v>0.676</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
@@ -2866,49 +2933,49 @@
         <v>80.5</v>
       </c>
       <c r="K14" t="n">
-        <v>0.476</v>
+        <v>0.477</v>
       </c>
       <c r="L14" t="n">
         <v>7.5</v>
       </c>
       <c r="M14" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="N14" t="n">
-        <v>0.354</v>
+        <v>0.355</v>
       </c>
       <c r="O14" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="P14" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.706</v>
+        <v>0.707</v>
       </c>
       <c r="R14" t="n">
         <v>11.4</v>
       </c>
       <c r="S14" t="n">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="T14" t="n">
         <v>41.5</v>
       </c>
       <c r="U14" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="V14" t="n">
         <v>14.9</v>
       </c>
       <c r="W14" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="X14" t="n">
         <v>5.8</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Z14" t="n">
         <v>20.9</v>
@@ -2920,10 +2987,10 @@
         <v>100.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="AE14" t="n">
         <v>5</v>
@@ -2932,16 +2999,16 @@
         <v>4</v>
       </c>
       <c r="AG14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH14" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AI14" t="n">
         <v>5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK14" t="n">
         <v>4</v>
@@ -2950,7 +3017,7 @@
         <v>11</v>
       </c>
       <c r="AM14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AN14" t="n">
         <v>21</v>
@@ -2989,7 +3056,7 @@
         <v>5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA14" t="n">
         <v>8</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-26-2012-13</t>
+          <t>2013-03-26</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>0.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE15" t="n">
         <v>14</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-26-2012-13</t>
+          <t>2013-03-26</t>
         </is>
       </c>
     </row>
@@ -3287,13 +3354,13 @@
         <v>3.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE16" t="n">
         <v>6</v>
       </c>
       <c r="AF16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG16" t="n">
         <v>6</v>
@@ -3356,7 +3423,7 @@
         <v>17</v>
       </c>
       <c r="BA16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB16" t="n">
         <v>26</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-26-2012-13</t>
+          <t>2013-03-26</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>8</v>
       </c>
       <c r="AD17" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3496,7 +3563,7 @@
         <v>6</v>
       </c>
       <c r="AM17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AN17" t="n">
         <v>2</v>
@@ -3514,13 +3581,13 @@
         <v>28</v>
       </c>
       <c r="AS17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT17" t="n">
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV17" t="n">
         <v>3</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-26-2012-13</t>
+          <t>2013-03-26</t>
         </is>
       </c>
     </row>
@@ -3651,16 +3718,16 @@
         <v>-1.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF18" t="n">
         <v>15</v>
       </c>
       <c r="AG18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH18" t="n">
         <v>15</v>
@@ -3681,7 +3748,7 @@
         <v>18</v>
       </c>
       <c r="AN18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO18" t="n">
         <v>24</v>
@@ -3720,7 +3787,7 @@
         <v>9</v>
       </c>
       <c r="BA18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB18" t="n">
         <v>12</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-26-2012-13</t>
+          <t>2013-03-26</t>
         </is>
       </c>
     </row>
@@ -3755,43 +3822,43 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F19" t="n">
         <v>44</v>
       </c>
       <c r="G19" t="n">
-        <v>0.362</v>
+        <v>0.353</v>
       </c>
       <c r="H19" t="n">
         <v>48.1</v>
       </c>
       <c r="I19" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="J19" t="n">
         <v>81.59999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.437</v>
+        <v>0.436</v>
       </c>
       <c r="L19" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="M19" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3</v>
+        <v>0.294</v>
       </c>
       <c r="O19" t="n">
-        <v>18.2</v>
+        <v>18.4</v>
       </c>
       <c r="P19" t="n">
-        <v>24.8</v>
+        <v>25.1</v>
       </c>
       <c r="Q19" t="n">
         <v>0.732</v>
@@ -3815,28 +3882,28 @@
         <v>8.1</v>
       </c>
       <c r="X19" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y19" t="n">
         <v>5.9</v>
       </c>
       <c r="Z19" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>95</v>
+        <v>94.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>-2.6</v>
+        <v>-3</v>
       </c>
       <c r="AD19" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AE19" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AF19" t="n">
         <v>21</v>
@@ -3848,13 +3915,13 @@
         <v>26</v>
       </c>
       <c r="AI19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ19" t="n">
         <v>16</v>
       </c>
       <c r="AK19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL19" t="n">
         <v>28</v>
@@ -3866,7 +3933,7 @@
         <v>30</v>
       </c>
       <c r="AO19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AP19" t="n">
         <v>6</v>
@@ -3881,7 +3948,7 @@
         <v>17</v>
       </c>
       <c r="AT19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU19" t="n">
         <v>16</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-26-2012-13</t>
+          <t>2013-03-26</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-3.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE20" t="n">
         <v>23</v>
@@ -4033,7 +4100,7 @@
         <v>22</v>
       </c>
       <c r="AJ20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK20" t="n">
         <v>12</v>
@@ -4087,7 +4154,7 @@
         <v>28</v>
       </c>
       <c r="BB20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC20" t="n">
         <v>23</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-26-2012-13</t>
+          <t>2013-03-26</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E21" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F21" t="n">
         <v>26</v>
       </c>
       <c r="G21" t="n">
-        <v>0.623</v>
+        <v>0.618</v>
       </c>
       <c r="H21" t="n">
         <v>48.1</v>
@@ -4137,22 +4204,22 @@
         <v>36</v>
       </c>
       <c r="J21" t="n">
-        <v>81.5</v>
+        <v>81.3</v>
       </c>
       <c r="K21" t="n">
         <v>0.442</v>
       </c>
       <c r="L21" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="M21" t="n">
         <v>28.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0.369</v>
+        <v>0.37</v>
       </c>
       <c r="O21" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="P21" t="n">
         <v>21.6</v>
@@ -4170,13 +4237,13 @@
         <v>40.9</v>
       </c>
       <c r="U21" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="V21" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="W21" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X21" t="n">
         <v>3.8</v>
@@ -4185,7 +4252,7 @@
         <v>4</v>
       </c>
       <c r="Z21" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="AA21" t="n">
         <v>19.4</v>
@@ -4194,10 +4261,10 @@
         <v>99</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AE21" t="n">
         <v>8</v>
@@ -4206,10 +4273,10 @@
         <v>7</v>
       </c>
       <c r="AG21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI21" t="n">
         <v>24</v>
@@ -4239,7 +4306,7 @@
         <v>16</v>
       </c>
       <c r="AR21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS21" t="n">
         <v>24</v>
@@ -4254,7 +4321,7 @@
         <v>1</v>
       </c>
       <c r="AW21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4263,10 +4330,10 @@
         <v>2</v>
       </c>
       <c r="AZ21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BB21" t="n">
         <v>11</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-26-2012-13</t>
+          <t>2013-03-26</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE22" t="n">
         <v>3</v>
@@ -4436,7 +4503,7 @@
         <v>29</v>
       </c>
       <c r="AW22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX22" t="n">
         <v>1</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-26-2012-13</t>
+          <t>2013-03-26</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-6.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE23" t="n">
         <v>29</v>
@@ -4612,7 +4679,7 @@
         <v>15</v>
       </c>
       <c r="AU23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV23" t="n">
         <v>12</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-26-2012-13</t>
+          <t>2013-03-26</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-3.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE24" t="n">
         <v>20</v>
@@ -4764,10 +4831,10 @@
         <v>6</v>
       </c>
       <c r="AK24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM24" t="n">
         <v>25</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-26-2012-13</t>
+          <t>2013-03-26</t>
         </is>
       </c>
     </row>
@@ -4925,13 +4992,13 @@
         <v>-6.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE25" t="n">
         <v>27</v>
       </c>
       <c r="AF25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG25" t="n">
         <v>27</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-26-2012-13</t>
+          <t>2013-03-26</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-1.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE26" t="n">
         <v>19</v>
@@ -5137,7 +5204,7 @@
         <v>4</v>
       </c>
       <c r="AN26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO26" t="n">
         <v>22</v>
@@ -5149,7 +5216,7 @@
         <v>7</v>
       </c>
       <c r="AR26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS26" t="n">
         <v>15</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-26-2012-13</t>
+          <t>2013-03-26</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-5.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE27" t="n">
         <v>23</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-26-2012-13</t>
+          <t>2013-03-26</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>7.9</v>
       </c>
       <c r="AD28" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE28" t="n">
         <v>2</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-26-2012-13</t>
+          <t>2013-03-26</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-2.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE29" t="n">
         <v>21</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-26-2012-13</t>
+          <t>2013-03-26</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-0.7</v>
       </c>
       <c r="AD30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE30" t="n">
         <v>16</v>
@@ -5868,7 +5935,7 @@
         <v>12</v>
       </c>
       <c r="AO30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP30" t="n">
         <v>7</v>
@@ -5883,7 +5950,7 @@
         <v>23</v>
       </c>
       <c r="AT30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU30" t="n">
         <v>13</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-26-2012-13</t>
+          <t>2013-03-26</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-2.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE31" t="n">
         <v>21</v>
@@ -6038,7 +6105,7 @@
         <v>17</v>
       </c>
       <c r="AK31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL31" t="n">
         <v>18</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-26-2012-13</t>
+          <t>2013-03-26</t>
         </is>
       </c>
     </row>
